--- a/users/input/AnPT/entities.xlsx
+++ b/users/input/AnPT/entities.xlsx
@@ -1,35 +1,203 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="entities" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="meta" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet sheetId="1" name="entities" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="meta" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+  <si>
+    <t>tickers</t>
+  </si>
+  <si>
+    <t>etfs</t>
+  </si>
+  <si>
+    <t>indices</t>
+  </si>
+  <si>
+    <t>exchanges</t>
+  </si>
+  <si>
+    <t>industries</t>
+  </si>
+  <si>
+    <t>entities</t>
+  </si>
+  <si>
+    <t>HPG</t>
+  </si>
+  <si>
+    <t>E1VFVN30</t>
+  </si>
+  <si>
+    <t>VNINDEX</t>
+  </si>
+  <si>
+    <t>HOSE</t>
+  </si>
+  <si>
+    <t>THEP</t>
+  </si>
+  <si>
+    <t>FPT</t>
+  </si>
+  <si>
+    <t>VN30</t>
+  </si>
+  <si>
+    <t>HNX</t>
+  </si>
+  <si>
+    <t>NGAN_HANG</t>
+  </si>
+  <si>
+    <t>VCB</t>
+  </si>
+  <si>
+    <t>UPINDEX</t>
+  </si>
+  <si>
+    <t>UPCOM</t>
+  </si>
+  <si>
+    <t>DAU_KHI</t>
+  </si>
+  <si>
+    <t>VNM</t>
+  </si>
+  <si>
+    <t>VNXALL</t>
+  </si>
+  <si>
+    <t>QUY</t>
+  </si>
+  <si>
+    <t>MWG</t>
+  </si>
+  <si>
+    <t>XAY_DUNG</t>
+  </si>
+  <si>
+    <t>AAA</t>
+  </si>
+  <si>
+    <t>CONG_TY_CHUNG_KHOAN</t>
+  </si>
+  <si>
+    <t>HCM</t>
+  </si>
+  <si>
+    <t>BAO_HIEM</t>
+  </si>
+  <si>
+    <t>VIC</t>
+  </si>
+  <si>
+    <t>DIEN</t>
+  </si>
+  <si>
+    <t>SSI</t>
+  </si>
+  <si>
+    <t>NUOC</t>
+  </si>
+  <si>
+    <t>OIL</t>
+  </si>
+  <si>
+    <t>PHAN_BON</t>
+  </si>
+  <si>
+    <t>BSR</t>
+  </si>
+  <si>
+    <t>THUC_PHAM</t>
+  </si>
+  <si>
+    <t>VHM</t>
+  </si>
+  <si>
+    <t>VAN_TAI</t>
+  </si>
+  <si>
+    <t>GMD</t>
+  </si>
+  <si>
+    <t>BAN_LE</t>
+  </si>
+  <si>
+    <t>VIB</t>
+  </si>
+  <si>
+    <t>VPB</t>
+  </si>
+  <si>
+    <t>CONG_NGHE</t>
+  </si>
+  <si>
+    <t>BID</t>
+  </si>
+  <si>
+    <t>CTG</t>
+  </si>
+  <si>
+    <t>VIX</t>
+  </si>
+  <si>
+    <t>TLG</t>
+  </si>
+  <si>
+    <t>PET</t>
+  </si>
+  <si>
+    <t>DHA</t>
+  </si>
+  <si>
+    <t>LPB</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>AnPT</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>industries dung CODE nganh GICS</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,80 +216,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -200,6 +309,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -234,6 +344,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -268,20 +379,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -403,163 +510,510 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>tickers</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>etfs</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>indices</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>exchanges</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>industries</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>entities</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HPG</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>E1VFVN30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>VNINDEX</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>THEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>FPT</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VN30</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>NGAN_HANG</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>VCB</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>VNM</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MWG</t>
-        </is>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>user</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AnPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>industries dung CODE nganh GICS</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010088BB270C8F5FC24BA49AFFE556196667" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bebf88d6575d16559b5f30f0a2a701c1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c36903d5-5ed0-4454-a196-b1a2f9ebaa03" xmlns:ns3="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7261e384d67fa0b6a688911c7473044a" ns2:_="" ns3:_="">
+    <xsd:import namespace="c36903d5-5ed0-4454-a196-b1a2f9ebaa03"/>
+    <xsd:import namespace="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c36903d5-5ed0-4454-a196-b1a2f9ebaa03" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="8f7c344f-19d0-4f45-b23a-2df2b546d212" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{4dc7bc77-2376-40bf-86a0-4a9e9b5c2537}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c36903d5-5ed0-4454-a196-b1a2f9ebaa03">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AB6AC7D-C1F2-470A-9194-211439F98A6D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5623A7CA-EEA5-49DD-935B-8939F7AAC0FA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A28B31-26C0-40DD-B646-8E1BFB3E6177}"/>
 </file>
--- a/users/input/AnPT/entities.xlsx
+++ b/users/input/AnPT/entities.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
   <si>
     <t>tickers</t>
   </si>
@@ -162,6 +162,21 @@
   </si>
   <si>
     <t>LPB</t>
+  </si>
+  <si>
+    <t>GEX</t>
+  </si>
+  <si>
+    <t>HDB</t>
+  </si>
+  <si>
+    <t>STB</t>
+  </si>
+  <si>
+    <t>VCI</t>
+  </si>
+  <si>
+    <t>VCK</t>
   </si>
   <si>
     <t>key</t>
@@ -556,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
@@ -759,6 +774,31 @@
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -777,26 +817,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1007,13 +1047,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AB6AC7D-C1F2-470A-9194-211439F98A6D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96D459AD-085C-45CA-B3D7-FE3598BE0A23}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5623A7CA-EEA5-49DD-935B-8939F7AAC0FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8092EEB6-03BC-49B2-AF08-23C220E810B6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A28B31-26C0-40DD-B646-8E1BFB3E6177}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B832AE4-6A1F-497E-AE36-6A70CF8528A1}"/>
 </file>